--- a/vault-dalarna-university/03 IKS/Analys/Innehåll.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Innehåll.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Innehåll" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Innehåll'!$A$1:$E$305</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6601,7 +6601,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6611,24 +6611,24 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Stub/platshållare</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (429 tecken): Den studerande planerar och genomför undervisning i den verksamhetsförlagda utbildningen. Didaktiska frågor och utmaning…</t>
+          <t>Osannolikt kort (16 tecken): 'Innehåll saknas.'</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6643,19 +6643,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (637 tecken): I kursen integreras ämneskunskaper och utbildningsvetenskap och den studerande tar ett självständigt helhetsansvar för p…</t>
+          <t>4 meningar i ett stycke (429 tecken): Den studerande planerar och genomför undervisning i den verksamhetsförlagda utbildningen. Didaktiska frågor och utmaning…</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6670,19 +6670,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (620 tecken): I kursen undersöks den egna skolans systematiska kvalitetsarbete samt olika arenor för lärares och övrig personals läran…</t>
+          <t>4 meningar i ett stycke (637 tecken): I kursen integreras ämneskunskaper och utbildningsvetenskap och den studerande tar ett självständigt helhetsansvar för p…</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GPG3JC</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6697,19 +6697,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (411 tecken): I kursen behandlas hur nutida utbildning för barn och ungdomar organiseras och styrs i Sverige, med viss historisk övers…</t>
+          <t>4 meningar i ett stycke (620 tecken): I kursen undersöks den egna skolans systematiska kvalitetsarbete samt olika arenor för lärares och övrig personals läran…</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GPG3JP</t>
+          <t>GPG3JC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (1028 tecken): Kursen kombinerar nätbaserade och campusförlagda lärandeaktiviteter där studenter samarbetar i internationellt blandade …</t>
+          <t>4 meningar i ett stycke (411 tecken): I kursen behandlas hur nutida utbildning för barn och ungdomar organiseras och styrs i Sverige, med viss historisk övers…</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JC</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG3JP</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1096 tecken): Genomförandet av examensarbetet bygger på att den studerande tidigare i lärarutbildningen anslutit till något av högskol…</t>
+          <t>6 meningar i ett stycke (1028 tecken): Kursen kombinerar nätbaserade och campusförlagda lärandeaktiviteter där studenter samarbetar i internationellt blandade …</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JP</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6783,14 +6783,14 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1107 tecken): Genomförandet av examensarbetet bygger på att den studerande tidigare i lärarutbildningen anslutit till något av högskol…</t>
+          <t>9 meningar i ett stycke (1096 tecken): Genomförandet av examensarbetet bygger på att den studerande tidigare i lärarutbildningen anslutit till något av högskol…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (744 tecken): I kursen behandlas begrepp som normalitet, inkludering, barn i behov av särskilt stöd, formativ och summativ bedömning. …</t>
+          <t>9 meningar i ett stycke (1107 tecken): Genomförandet av examensarbetet bygger på att den studerande tidigare i lärarutbildningen anslutit till något av högskol…</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6859,19 +6859,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (759 tecken): I kursen behandlas begrepp som normalitet, inkludering, barn i behov av särskilt stöd, formativ och summativ bedömning. …</t>
+          <t>6 meningar i ett stycke (744 tecken): I kursen behandlas begrepp som normalitet, inkludering, barn i behov av särskilt stöd, formativ och summativ bedömning. …</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6886,24 +6886,24 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (665 tecken): Under kursen planerar och genomför den studerande självständigt och i samråd med handledare en undersökning av vetenskap…</t>
+          <t>6 meningar i ett stycke (759 tecken): I kursen behandlas begrepp som normalitet, inkludering, barn i behov av särskilt stöd, formativ och summativ bedömning. …</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (473 tecken): I kursen studeras kabbala, judisk mystik och chassidism i ett religionshistoriskt perspektiv och satt i en större rabbin…</t>
+          <t>4 meningar i ett stycke (665 tecken): Under kursen planerar och genomför den studerande självständigt och i samråd med handledare en undersökning av vetenskap…</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6940,19 +6940,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (648 tecken): Denna kurs behandlar upplevelser av osynlig närvaro i religiösa, andliga och populärkulturella sammanhang. Kursen fokuse…</t>
+          <t>4 meningar i ett stycke (473 tecken): I kursen studeras kabbala, judisk mystik och chassidism i ett religionshistoriskt perspektiv och satt i en större rabbin…</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ARK29M</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (579 tecken): I kursen genomförs under handledning en kvalificerad och självständig vetenskaplig undersökning med utgångspunkt i ett f…</t>
+          <t>5 meningar i ett stycke (648 tecken): Denna kurs behandlar upplevelser av osynlig närvaro i religiösa, andliga och populärkulturella sammanhang. Kursen fokuse…</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>ARK29M</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6994,19 +6994,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (576 tecken): Kursen innebär ett utförande av examensarbete med temat mänskliga rättigheter. Mänskliga rättigheter har blivit ett domi…</t>
+          <t>4 meningar i ett stycke (579 tecken): I kursen genomförs under handledning en kvalificerad och självständig vetenskaplig undersökning med utgångspunkt i ett f…</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29M</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (436 tecken): Kursen behandlar berättelser som fenomen, som meningsskapande och identitetsskapande på kollektiv- och individnivå samt …</t>
+          <t>5 meningar i ett stycke (576 tecken): Kursen innebär ett utförande av examensarbete med temat mänskliga rättigheter. Mänskliga rättigheter har blivit ett domi…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (600 tecken): I kursen behandlas och diskuteras möjliga svar på de didaktiska frågorna om urval av undervisningsinnehåll, undervisning…</t>
+          <t>4 meningar i ett stycke (436 tecken): Kursen behandlar berättelser som fenomen, som meningsskapande och identitetsskapande på kollektiv- och individnivå samt …</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GRK36J</t>
+          <t>GRK32C</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (660 tecken): Kursen behandlar det samtida fenomen där religionslika rörelser vuxit fram ur populärkultur och fiktiva berättelser. Exe…</t>
+          <t>4 meningar i ett stycke (600 tecken): I kursen behandlas och diskuteras möjliga svar på de didaktiska frågorna om urval av undervisningsinnehåll, undervisning…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>GRK36J</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7102,19 +7102,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>6 meningar i ett stycke (659 tecken): Denna kurs vänder sig till lärare på grund- och gymnasieskolor. Den behandlar olika former av rollspel i relation till ä…</t>
+          <t>6 meningar i ett stycke (660 tecken): Kursen behandlar det samtida fenomen där religionslika rörelser vuxit fram ur populärkultur och fiktiva berättelser. Exe…</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7129,19 +7129,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (598 tecken): I kursen planeras ett fältarbete och det skrivs en förberedande forskningsplan för ett fältstudium enligt modellen _Mino…</t>
+          <t>6 meningar i ett stycke (659 tecken): Denna kurs vänder sig till lärare på grund- och gymnasieskolor. Den behandlar olika former av rollspel i relation till ä…</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7156,24 +7156,24 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (700 tecken): I kursen studeras och analyseras villkoren för människors kulturella identitet som påverkas av en ökande närvaro av medi…</t>
+          <t>4 meningar i ett stycke (598 tecken): I kursen planeras ett fältarbete och det skrivs en förberedande forskningsplan för ett fältstudium enligt modellen _Mino…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7183,19 +7183,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (749 tecken): Kursen behandlar svensk och europeisk IT-rätt och rättsliga frågor som är av betydelse i samband med utveckling och anvä…</t>
+          <t>4 meningar i ett stycke (700 tecken): I kursen studeras och analyseras villkoren för människors kulturella identitet som påverkas av en ökande närvaro av medi…</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (888 tecken): Kursen ger en inblick i juridisk systematik och metod. Utformningen av kursen anknyter till juridiska frågeställningar a…</t>
+          <t>4 meningar i ett stycke (749 tecken): Kursen behandlar svensk och europeisk IT-rätt och rättsliga frågor som är av betydelse i samband med utveckling och anvä…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (608 tecken): Kursen behandlar grundläggande straffrättslig bevisning främst med tillämpning på databrott såsom säkring, analys, prese…</t>
+          <t>7 meningar i ett stycke (888 tecken): Kursen ger en inblick i juridisk systematik och metod. Utformningen av kursen anknyter till juridiska frågeställningar a…</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7264,19 +7264,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>9 meningar i ett stycke (1282 tecken): Kursen behandlar juridisk metod inklusive grundläggande juridiska begrepp och definitioner, det svenska rättssystemets u…</t>
+          <t>5 meningar i ett stycke (608 tecken): Kursen behandlar grundläggande straffrättslig bevisning främst med tillämpning på databrott såsom säkring, analys, prese…</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7291,19 +7291,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (636 tecken): Kursen ger en introduktion till juridiken och behandlar de rättsområden som är av betydelse i samband med användning av …</t>
+          <t>9 meningar i ett stycke (1282 tecken): Kursen behandlar juridisk metod inklusive grundläggande juridiska begrepp och definitioner, det svenska rättssystemets u…</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7318,19 +7318,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (482 tecken): Kursen behandlar den kriminologiska sidan av IT-brottslighet och skall ge svar på frågan varför människor begår brott me…</t>
+          <t>5 meningar i ett stycke (636 tecken): Kursen ger en introduktion till juridiken och behandlar de rättsområden som är av betydelse i samband med användning av …</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7345,19 +7345,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (768 tecken): Kursen ger en introduktion till juridiken och behandlar de rättsområden som är av betydelse i en digital miljö, främst I…</t>
+          <t>4 meningar i ett stycke (482 tecken): Kursen behandlar den kriminologiska sidan av IT-brottslighet och skall ge svar på frågan varför människor begår brott me…</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7372,24 +7372,24 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (546 tecken): Kursen belyser relevanta rättsregler specifikt från det idrottsliga perspektivet. Frågor som särskilt lyfts fram är idro…</t>
+          <t>8 meningar i ett stycke (768 tecken): Kursen ger en introduktion till juridiken och behandlar de rättsområden som är av betydelse i en digital miljö, främst I…</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>ASK22H</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7399,19 +7399,19 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (713 tecken): Kursen innehåller en teoretisk och empirisk fördjupning av begreppen stat och nation, samt en överblick över utvecklinge…</t>
+          <t>4 meningar i ett stycke (546 tecken): Kursen belyser relevanta rättsregler specifikt från det idrottsliga perspektivet. Frågor som särskilt lyfts fram är idro…</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>ASK22J</t>
+          <t>ASK22H</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7426,19 +7426,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (468 tecken): Kursen fokuserar centrala teoribildningar kopplade till demokratibegreppet. Demokratisering och återgång till auktoritär…</t>
+          <t>5 meningar i ett stycke (713 tecken): Kursen innehåller en teoretisk och empirisk fördjupning av begreppen stat och nation, samt en överblick över utvecklinge…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22H</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>ASK22K</t>
+          <t>ASK22J</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7453,19 +7453,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (606 tecken): I kursen behandlas begrepp och teorier om politisk kultur. Här inbegrips såväl innebörden av politisk kultur som förändr…</t>
+          <t>4 meningar i ett stycke (468 tecken): Kursen fokuserar centrala teoribildningar kopplade till demokratibegreppet. Demokratisering och återgång till auktoritär…</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22J</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>ASK297</t>
+          <t>ASK22K</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7480,19 +7480,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (453 tecken): Kursen fokuserar på komparativa metoder applicerade på afrikanska förhållanden. I kursen studeras olika typer av kompara…</t>
+          <t>5 meningar i ett stycke (606 tecken): I kursen behandlas begrepp och teorier om politisk kultur. Här inbegrips såväl innebörden av politisk kultur som förändr…</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22K</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GSK2C9</t>
+          <t>ASK297</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7507,19 +7507,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (474 tecken): I kursen studeras det svenska civilsamhället däribland dess historiska framväxt, omfattning och roll i och för demokrati…</t>
+          <t>4 meningar i ett stycke (453 tecken): Kursen fokuserar på komparativa metoder applicerade på afrikanska förhållanden. I kursen studeras olika typer av kompara…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK297</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>GSK2C9</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7534,19 +7534,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (634 tecken): I kursen kommer den samtida segregationen i Sverige att studeras och diskuteras utifrån ett historiskt och internationel…</t>
+          <t>4 meningar i ett stycke (474 tecken): I kursen studeras det svenska civilsamhället däribland dess historiska framväxt, omfattning och roll i och för demokrati…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2C9</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7561,19 +7561,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (478 tecken): I kursen behandlas politiskt deltagande och dess roll och betydelse i och för demokratin. Dessutom studeras olika former…</t>
+          <t>4 meningar i ett stycke (634 tecken): I kursen kommer den samtida segregationen i Sverige att studeras och diskuteras utifrån ett historiskt och internationel…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7588,19 +7588,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (636 tecken): Kursen belyser den historiska framväxten och förändringen av EU med fokus på integrationsprocesserna från olika integrat…</t>
+          <t>4 meningar i ett stycke (478 tecken): I kursen behandlas politiskt deltagande och dess roll och betydelse i och för demokratin. Dessutom studeras olika former…</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7615,19 +7615,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (407 tecken): I kursen introduceras den offentliga förvaltningens roll och organisation i svenska politiska systemet. Fokus riktas bla…</t>
+          <t>4 meningar i ett stycke (636 tecken): Kursen belyser den historiska framväxten och förändringen av EU med fokus på integrationsprocesserna från olika integrat…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7642,19 +7642,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (548 tecken): I kursen ingår förberedelser för ett självständigt uppsatsarbete genom att den studerande tränas i att söka, sammanfatta…</t>
+          <t>4 meningar i ett stycke (407 tecken): I kursen introduceras den offentliga förvaltningens roll och organisation i svenska politiska systemet. Fokus riktas bla…</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7669,19 +7669,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (601 tecken): I kursen diskuteras EU:s roll i den globala politiken där särskilt EU:s utrikes- och säkerhetspolitik belyses utifrån et…</t>
+          <t>4 meningar i ett stycke (548 tecken): I kursen ingår förberedelser för ett självständigt uppsatsarbete genom att den studerande tränas i att söka, sammanfatta…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7696,19 +7696,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (618 tecken): Kursen belyser den historiska framväxten av EU med fokus på integrationsprocesserna från olika integrationsteoretiska pe…</t>
+          <t>5 meningar i ett stycke (601 tecken): I kursen diskuteras EU:s roll i den globala politiken där särskilt EU:s utrikes- och säkerhetspolitik belyses utifrån et…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>SK2011</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7723,24 +7723,24 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (639 tecken): I kursen behandlas centrala frågeställningar, begrepp och teorier inom forskningsfältet freds- och konfliktstudier. Dess…</t>
+          <t>4 meningar i ett stycke (618 tecken): Kursen belyser den historiska framväxten av EU med fokus på integrationsprocesserna från olika integrationsteoretiska pe…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>SO1047</t>
+          <t>SK2011</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (431 tecken): I kursen behandlas olika organisationsformer och teorier med en sociologisk belysning. Vidare behandlas gruppdynamiska p…</t>
+          <t>4 meningar i ett stycke (639 tecken): I kursen behandlas centrala frågeställningar, begrepp och teorier inom forskningsfältet freds- och konfliktstudier. Dess…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2011</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>SO1047</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -7777,19 +7777,19 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (828 tecken): Den här kursen handlar om hur en mer hållbar, robust och relevant turismnäring kan skapas. Kursen erbjuder yrkesverksamm…</t>
+          <t>4 meningar i ett stycke (431 tecken): I kursen behandlas olika organisationsformer och teorier med en sociologisk belysning. Vidare behandlas gruppdynamiska p…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1047</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (496 tecken): Kursen utforskar hur olika aktörer förhåller sig till katastrofer utlösta av miljömässiga-, sociala- och ekonomiska kris…</t>
+          <t>5 meningar i ett stycke (828 tecken): Den här kursen handlar om hur en mer hållbar, robust och relevant turismnäring kan skapas. Kursen erbjuder yrkesverksamm…</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>ATR2AF</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7831,19 +7831,19 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (744 tecken): Kursen består av två moduler. Den första modulen handlar om destinationsmarknadsföringens kontext samt dess strategier. …</t>
+          <t>4 meningar i ett stycke (496 tecken): Kursen utforskar hur olika aktörer förhåller sig till katastrofer utlösta av miljömässiga-, sociala- och ekonomiska kris…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>ATR2BB</t>
+          <t>ATR2AF</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7858,19 +7858,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (886 tecken): I kursen genomförs en kvalificerad och självständig vetenskaplig undersökning med utgångspunkt i ett formulerat turismve…</t>
+          <t>7 meningar i ett stycke (744 tecken): Kursen består av två moduler. Den första modulen handlar om destinationsmarknadsföringens kontext samt dess strategier. …</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2AF</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>ATR2BB</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7885,19 +7885,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (1136 tecken): I denna kurs utvecklas färdigheter och kunskaper i att identifiera och analysera verkliga problem inom turism, besöksnär…</t>
+          <t>5 meningar i ett stycke (886 tecken): I kursen genomförs en kvalificerad och självständig vetenskaplig undersökning med utgångspunkt i ett formulerat turismve…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BB</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7912,19 +7912,19 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (698 tecken): Kursen introducerar studenterna till grundläggande forskningsförmågor. Med hjälp av teoretiska ramverk och begrepp inom …</t>
+          <t>7 meningar i ett stycke (1136 tecken): I denna kurs utvecklas färdigheter och kunskaper i att identifiera och analysera verkliga problem inom turism, besöksnär…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7939,19 +7939,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (781 tecken): Denna kurs behandlar upplevelser och utveckling av upplevelser, i turismsammanhang. Skillnaderna mellan turismprodukter,…</t>
+          <t>5 meningar i ett stycke (698 tecken): Kursen introducerar studenterna till grundläggande forskningsförmågor. Med hjälp av teoretiska ramverk och begrepp inom …</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7966,19 +7966,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>8 meningar i ett stycke (683 tecken): Kursen syftar till att introducera kvantitativa forskningsmetoder. Kursen består av två delar. I första delen belyses in…</t>
+          <t>7 meningar i ett stycke (781 tecken): Denna kurs behandlar upplevelser och utveckling av upplevelser, i turismsammanhang. Skillnaderna mellan turismprodukter,…</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7993,19 +7993,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (618 tecken): Syftet med kursen är att bekanta studenterna med kvalitativa forskningsundersökningar och utrusta dem med metodkunskap i…</t>
+          <t>8 meningar i ett stycke (683 tecken): Kursen syftar till att introducera kvantitativa forskningsmetoder. Kursen består av två delar. I första delen belyses in…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (786 tecken): Kursen behandlar förhållandet mellan samtida turism- och samhällsfrågor samt aktuell, världsledande turismforskning. Fok…</t>
+          <t>4 meningar i ett stycke (618 tecken): Syftet med kursen är att bekanta studenterna med kvalitativa forskningsundersökningar och utrusta dem med metodkunskap i…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (679 tecken): Kursen utgår från att studenten i samråd med akademisk handledare och representant från verksamheten fastställer ett pro…</t>
+          <t>5 meningar i ett stycke (786 tecken): Kursen behandlar förhållandet mellan samtida turism- och samhällsfrågor samt aktuell, världsledande turismforskning. Fok…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (496 tecken): Denna kurs behandlar de multidisciplinära egenskaperna hos evenemang och festivaler samt evenemangens betydelse i samtid…</t>
+          <t>5 meningar i ett stycke (679 tecken): Kursen utgår från att studenten i samråd med akademisk handledare och representant från verksamheten fastställer ett pro…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8101,19 +8101,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (628 tecken): Kursen behandlar multidisciplinära perspektiv på hållbar design, förvaltning, övervakning och marknadsföring av naturbas…</t>
+          <t>4 meningar i ett stycke (496 tecken): Denna kurs behandlar de multidisciplinära egenskaperna hos evenemang och festivaler samt evenemangens betydelse i samtid…</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (652 tecken): Kursen fokuserar på frågor om hållbarhet, destinationsutveckling och globala trender inom turismutveckling och introduce…</t>
+          <t>4 meningar i ett stycke (628 tecken): Kursen behandlar multidisciplinära perspektiv på hållbar design, förvaltning, övervakning och marknadsföring av naturbas…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GTR3A4</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (476 tecken): Kursen introducerar kvantitativa forskningsmetoder och kursen består av tre moduler. I den första modulen behandlas olik…</t>
+          <t>4 meningar i ett stycke (652 tecken): Kursen fokuserar på frågor om hållbarhet, destinationsutveckling och globala trender inom turismutveckling och introduce…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GTR3AU</t>
+          <t>GTR3A4</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (512 tecken): Kursen har två moduler. Den första modulen introducerar grundläggande marknadsföringskoncept och teorier. Modulen tar up…</t>
+          <t>4 meningar i ett stycke (476 tecken): Kursen introducerar kvantitativa forskningsmetoder och kursen består av tre moduler. I den första modulen behandlas olik…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3AU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3A4</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GTR3AU</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (623 tecken): Kursen behandlar olika kulturella aspekter till exempel värderingar, övertygelser och antaganden och hur dessa påverkar …</t>
+          <t>5 meningar i ett stycke (512 tecken): Kursen har två moduler. Den första modulen introducerar grundläggande marknadsföringskoncept och teorier. Modulen tar up…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3AU</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (550 tecken): Kursen tar upp turismen roll i samhället med ett särskilt fokus på samhälleliga och ekonomiska aspekter i vid mening. De…</t>
+          <t>4 meningar i ett stycke (623 tecken): Kursen behandlar olika kulturella aspekter till exempel värderingar, övertygelser och antaganden och hur dessa påverkar …</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (556 tecken): Kursen bygger på övningar i att genomföra lokaliseringsanalyser baserat på kundunderlag för olika typer av serviceproduk…</t>
+          <t>4 meningar i ett stycke (550 tecken): Kursen tar upp turismen roll i samhället med ett särskilt fokus på samhälleliga och ekonomiska aspekter i vid mening. De…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8290,19 +8290,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (570 tecken): I kursen ges en introduktion till kartografi, korologi och GIS (Geografiska Informationssystem). Kursen behandlar översi…</t>
+          <t>4 meningar i ett stycke (556 tecken): Kursen bygger på övningar i att genomföra lokaliseringsanalyser baserat på kundunderlag för olika typer av serviceproduk…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (541 tecken): Kursen inleds med diskusisoner kring olika sorters tjänster, deras karaktäristik och betydelse i samhället med särskild …</t>
+          <t>4 meningar i ett stycke (570 tecken): I kursen ges en introduktion till kartografi, korologi och GIS (Geografiska Informationssystem). Kursen behandlar översi…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8349,14 +8349,14 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>7 meningar i ett stycke (789 tecken): Kursen behandlar turismens roll i samhället. Utveckling av turismen i olika delar av världen analyseras utifrån den glob…</t>
+          <t>4 meningar i ett stycke (541 tecken): Kursen inleds med diskusisoner kring olika sorters tjänster, deras karaktäristik och betydelse i samhället med särskild …</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8393,29 +8393,29 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ostyckad textmassa</t>
+          <t>Modulrubrik utan hp</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (726 tecken): Kursen utgår från att studenten i samråd med handledare från företag och akademi fastställer ett strategiskt utvecklings…</t>
+          <t>Modulrubrik utan hp-angivelse: 'modul 1'</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8425,24 +8425,24 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (439 tecken): Kursen behandlar utbildningspolitik samt utbildningens roll för utvecklingen av afrikanska samhällen. Fokus i kursen är …</t>
+          <t>7 meningar i ett stycke (789 tecken): Kursen behandlar turismens roll i samhället. Utveckling av turismen i olika delar av världen analyseras utifrån den glob…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8452,19 +8452,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (640 tecken): Studenten genomför ett studium av ett urval av Afrikas religioner. Kristendomens olika riktningar liksom islam och grund…</t>
+          <t>5 meningar i ett stycke (726 tecken): Kursen utgår från att studenten i samråd med handledare från företag och akademi fastställer ett strategiskt utvecklings…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>AS2001</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (430 tecken): Kursen behandlar utbildningspolitik samt utbildningens roll för utvecklingen av afrikanska samhällen. Fokus i kursen är …</t>
+          <t>5 meningar i ett stycke (439 tecken): Kursen behandlar utbildningspolitik samt utbildningens roll för utvecklingen av afrikanska samhällen. Fokus i kursen är …</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>AS2003</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,19 +8506,19 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (650 tecken): Studenten genomför ett fördjupat studium av ett urval av Afrikas religioner. Kristendomens olika riktningar liksom islam…</t>
+          <t>4 meningar i ett stycke (640 tecken): Studenten genomför ett studium av ett urval av Afrikas religioner. Kristendomens olika riktningar liksom islam och grund…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>AS3001</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8533,19 +8533,19 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (529 tecken): Kursen inleds med seminarier för genomgång av forskningsprocessen som innefattar ämnesval, problemställning, metod- och …</t>
+          <t>5 meningar i ett stycke (430 tecken): Kursen behandlar utbildningspolitik samt utbildningens roll för utvecklingen av afrikanska samhällen. Fokus i kursen är …</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>AS3003</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8560,19 +8560,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>5 meningar i ett stycke (961 tecken): Kursen behandlar nyckelfrågor rörande politik i samtida Afrika, där politik förstås som de antaganden och principer som …</t>
+          <t>4 meningar i ett stycke (650 tecken): Studenten genomför ett fördjupat studium av ett urval av Afrikas religioner. Kristendomens olika riktningar liksom islam…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>AS3005</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8587,44 +8587,98 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>4 meningar i ett stycke (525 tecken): I denna kurs behandlas olika humanistiska, samhällsvetenskapliga och utbildningsvetenskapliga vetenskapsteoretiska och v…</t>
+          <t>4 meningar i ett stycke (529 tecken): Kursen inleds med seminarier för genomgång av forskningsprocessen som innefattar ämnesval, problemställning, metod- och …</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>5 meningar i ett stycke (961 tecken): Kursen behandlar nyckelfrågor rörande politik i samtida Afrika, där politik förstås som de antaganden och principer som …</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>4 meningar i ett stycke (525 tecken): I denna kurs behandlas olika humanistiska, samhällsvetenskapliga och utbildningsvetenskapliga vetenskapsteoretiska och v…</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
           <t>AS4004</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Ostyckad textmassa</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Ostyckad textmassa</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
         <is>
           <t>4 meningar i ett stycke (542 tecken): Kursen inleds med en genomgång av forskningsprocessen som innefattar ämnesval, problemställning, metod- och teorianknytn…</t>
         </is>
       </c>
-      <c r="E303" s="2" t="inlineStr">
+      <c r="E305" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E303"/>
+  <autoFilter ref="A1:E305"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -9230,6 +9284,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId602"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A303" r:id="rId603"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A304" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A305" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId608"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
